--- a/data/trans_dic/IP18A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,05; 30,73</t>
+          <t>17,93; 31,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 28,76</t>
+          <t>16,1; 28,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,09; 24,91</t>
+          <t>12,58; 24,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,01; 45,33</t>
+          <t>7,96; 42,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 28,54</t>
+          <t>17,29; 29,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 25,55</t>
+          <t>14,94; 26,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 22,1</t>
+          <t>11,25; 22,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 26,69</t>
+          <t>2,38; 23,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 28,16</t>
+          <t>18,65; 27,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,77; 25,1</t>
+          <t>16,89; 25,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 20,99</t>
+          <t>13,4; 21,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 26,91</t>
+          <t>7,25; 25,39</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,25; 24,04</t>
+          <t>13,89; 23,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 22,06</t>
+          <t>13,61; 22,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,2; 23,73</t>
+          <t>14,31; 23,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 36,54</t>
+          <t>9,69; 36,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,97</t>
+          <t>16,24; 25,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 19,61</t>
+          <t>10,82; 19,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 22,45</t>
+          <t>13,68; 22,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 36,89</t>
+          <t>16,08; 37,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 23,3</t>
+          <t>16,57; 23,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,27; 19,1</t>
+          <t>13,14; 19,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,15</t>
+          <t>15,31; 21,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 32,02</t>
+          <t>16,72; 31,93</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,69; 31,39</t>
+          <t>19,15; 30,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 24,5</t>
+          <t>14,08; 24,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,52</t>
+          <t>14,42; 24,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 39,2</t>
+          <t>9,22; 36,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 24,98</t>
+          <t>14,06; 24,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,12; 25,28</t>
+          <t>15,5; 26,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,22; 31,14</t>
+          <t>19,77; 31,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 29,58</t>
+          <t>5,59; 30,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 26,21</t>
+          <t>17,56; 25,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,78</t>
+          <t>16,3; 23,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 26,26</t>
+          <t>18,26; 25,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 28,63</t>
+          <t>10,55; 28,6</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,78; 31,75</t>
+          <t>21,47; 32,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,16; 30,44</t>
+          <t>20,08; 30,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 24,75</t>
+          <t>15,43; 25,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 26,96</t>
+          <t>4,52; 27,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 23,77</t>
+          <t>14,78; 24,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 26,55</t>
+          <t>16,54; 26,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,93; 25,42</t>
+          <t>14,98; 24,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 34,87</t>
+          <t>9,11; 32,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 26,59</t>
+          <t>19,53; 26,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,17; 27,19</t>
+          <t>19,44; 26,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,22</t>
+          <t>16,33; 23,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 25,05</t>
+          <t>9,96; 26,33</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,14</t>
+          <t>20,6; 26,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,62; 23,67</t>
+          <t>18,39; 23,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,45</t>
+          <t>16,56; 21,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 25,97</t>
+          <t>13,49; 26,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 22,95</t>
+          <t>17,85; 22,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 21,33</t>
+          <t>16,33; 21,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,19</t>
+          <t>17,29; 22,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 25,5</t>
+          <t>13,64; 25,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,89; 23,62</t>
+          <t>19,73; 23,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 21,91</t>
+          <t>18,33; 21,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,03</t>
+          <t>17,53; 21,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,58</t>
+          <t>15,27; 23,54</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>27715</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28030</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22040</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3751</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29131</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28961</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22329</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>56846</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56991</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44368</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20718; 35972</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20667; 36275</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15452; 30589</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1358; 7183</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22301; 37582</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21718; 37896</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15225; 30349</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>515; 5155</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>45613; 67381</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>46235; 69295</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>34589; 56123</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2806; 9831</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>30398</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33269</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5798</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37528</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30505</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36982</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12851</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>67926</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63775</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73230</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>18650</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22970; 38365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>25826; 41835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27641; 44652</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2807; 10518</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>29226; 46714</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22143; 39856</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28552; 46227</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7997; 18828</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>57220; 80420</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>51826; 75975</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>61527; 84872</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>13161; 25135</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>30759</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27454</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26308</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5640</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31296</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35868</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>56214</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58749</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>62176</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10193</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>23855; 38386</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20072; 35631</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19761; 34025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2420; 9662</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18817; 32177</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24111; 40690</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28365; 44800</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1770; 9725</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>45367; 66340</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>48596; 71526</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>51224; 72677</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6113; 16567</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>50768</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51057</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37533</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>34451</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43438</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35856</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>85219</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>94495</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>73388</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>9476</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>41339; 62308</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>40614; 62680</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>29033; 47343</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1267; 7691</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>26791; 44251</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>33789; 53828</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>27311; 45121</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2597; 9285</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>73022; 98899</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>79043; 108198</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>60511; 87599</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5633; 14890</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>139640</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139810</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122128</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19229</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>25042</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>266205</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>274010</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>253163</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>44271</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>123195; 157361</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121942; 157901</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>106202; 137208</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13530; 26299</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>111383; 143189</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>115941; 151303</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>115814; 147761</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17947; 33365</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>241130; 288357</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>251680; 301133</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>229916; 277317</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>35401; 54582</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 31,13</t>
+          <t>18,12; 31,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 28,25</t>
+          <t>15,9; 27,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 24,91</t>
+          <t>12,46; 24,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 42,12</t>
+          <t>8,18; 42,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 29,13</t>
+          <t>16,94; 28,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 26,07</t>
+          <t>15,01; 25,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,25; 22,42</t>
+          <t>11,43; 23,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 23,79</t>
+          <t>2,28; 24,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,65; 27,55</t>
+          <t>18,98; 28,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,89; 25,31</t>
+          <t>16,62; 24,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 21,74</t>
+          <t>13,26; 21,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 25,39</t>
+          <t>8,1; 26,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,2</t>
+          <t>13,88; 23,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 22,04</t>
+          <t>13,69; 22,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,11</t>
+          <t>14,63; 23,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 36,3</t>
+          <t>10,32; 35,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 25,96</t>
+          <t>16,56; 25,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 19,48</t>
+          <t>11,2; 19,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 22,15</t>
+          <t>13,83; 22,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,08; 37,86</t>
+          <t>16,68; 37,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,57; 23,29</t>
+          <t>16,36; 23,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,14; 19,26</t>
+          <t>13,43; 19,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,12</t>
+          <t>15,18; 21,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 31,93</t>
+          <t>16,59; 32,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 30,81</t>
+          <t>19,13; 31,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,99</t>
+          <t>14,15; 24,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 24,83</t>
+          <t>14,51; 24,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 36,83</t>
+          <t>9,7; 36,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,05</t>
+          <t>14,09; 24,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 26,15</t>
+          <t>15,43; 25,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 31,22</t>
+          <t>19,44; 31,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 30,7</t>
+          <t>6,21; 30,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,56; 25,68</t>
+          <t>17,81; 25,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,3; 23,99</t>
+          <t>16,16; 23,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 25,91</t>
+          <t>18,43; 26,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 28,6</t>
+          <t>10,04; 27,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 32,36</t>
+          <t>22,06; 32,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,08; 30,99</t>
+          <t>20,1; 31,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 25,16</t>
+          <t>15,57; 24,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 27,42</t>
+          <t>6,26; 27,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,78; 24,41</t>
+          <t>14,67; 24,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 26,36</t>
+          <t>16,81; 25,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 24,75</t>
+          <t>15,1; 24,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 32,57</t>
+          <t>9,13; 31,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,53; 26,45</t>
+          <t>19,48; 26,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,44; 26,62</t>
+          <t>19,75; 26,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,64</t>
+          <t>16,23; 23,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 26,33</t>
+          <t>9,98; 26,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,6; 26,31</t>
+          <t>20,62; 26,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,81</t>
+          <t>18,41; 23,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,4</t>
+          <t>16,58; 21,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 26,22</t>
+          <t>13,56; 26,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 22,95</t>
+          <t>17,79; 22,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 21,32</t>
+          <t>16,39; 21,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,29; 22,06</t>
+          <t>16,97; 21,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 25,35</t>
+          <t>14,04; 24,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,73; 23,6</t>
+          <t>20,12; 23,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,93</t>
+          <t>18,23; 21,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 21,15</t>
+          <t>17,62; 21,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 23,54</t>
+          <t>14,7; 23,52</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20718; 35972</t>
+          <t>20941; 36364</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20667; 36275</t>
+          <t>20415; 35731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15452; 30589</t>
+          <t>15298; 30645</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1358; 7183</t>
+          <t>1395; 7215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22301; 37582</t>
+          <t>21847; 37322</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21718; 37896</t>
+          <t>21825; 37689</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15225; 30349</t>
+          <t>15476; 32187</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>515; 5155</t>
+          <t>494; 5292</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45613; 67381</t>
+          <t>46420; 68584</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46235; 69295</t>
+          <t>45492; 68236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34589; 56123</t>
+          <t>34230; 55148</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2806; 9831</t>
+          <t>3137; 10404</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22970; 38365</t>
+          <t>22947; 38864</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25826; 41835</t>
+          <t>25972; 42540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27641; 44652</t>
+          <t>28274; 44638</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2807; 10518</t>
+          <t>2989; 10170</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29226; 46714</t>
+          <t>29791; 46724</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22143; 39856</t>
+          <t>22919; 39777</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28552; 46227</t>
+          <t>28864; 46594</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7997; 18828</t>
+          <t>8297; 18785</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57220; 80420</t>
+          <t>56502; 80774</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51826; 75975</t>
+          <t>52957; 75740</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61527; 84872</t>
+          <t>61019; 84834</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13161; 25135</t>
+          <t>13058; 25457</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23855; 38386</t>
+          <t>23829; 38870</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20072; 35631</t>
+          <t>20179; 35142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19761; 34025</t>
+          <t>19878; 34041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2420; 9662</t>
+          <t>2546; 9553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18817; 32177</t>
+          <t>18857; 32940</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24111; 40690</t>
+          <t>24011; 39541</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28365; 44800</t>
+          <t>27904; 45407</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1770; 9725</t>
+          <t>1968; 9782</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45367; 66340</t>
+          <t>46010; 66005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48596; 71526</t>
+          <t>48179; 71329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51224; 72677</t>
+          <t>51718; 73916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6113; 16567</t>
+          <t>5815; 16122</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41339; 62308</t>
+          <t>42483; 62221</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40614; 62680</t>
+          <t>40655; 62967</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29033; 47343</t>
+          <t>29302; 46663</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1267; 7691</t>
+          <t>1756; 7753</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26791; 44251</t>
+          <t>26606; 43608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33789; 53828</t>
+          <t>34324; 52874</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27311; 45121</t>
+          <t>27528; 45009</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2597; 9285</t>
+          <t>2603; 9038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73022; 98899</t>
+          <t>72826; 99638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79043; 108198</t>
+          <t>80304; 109057</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60511; 87599</t>
+          <t>60152; 86972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5633; 14890</t>
+          <t>5647; 14860</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123195; 157361</t>
+          <t>123311; 156291</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121942; 157901</t>
+          <t>122091; 157209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106202; 137208</t>
+          <t>106331; 139069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13530; 26299</t>
+          <t>13605; 26560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>111383; 143189</t>
+          <t>110984; 143305</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>115941; 151303</t>
+          <t>116359; 152330</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>115814; 147761</t>
+          <t>113675; 147131</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17947; 33365</t>
+          <t>18472; 32847</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>241130; 288357</t>
+          <t>245853; 292357</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>251680; 301133</t>
+          <t>250288; 300829</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229916; 277317</t>
+          <t>231019; 277629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35401; 54582</t>
+          <t>34095; 54546</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21,83%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17,94%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,12; 31,47</t>
+          <t>17,21; 28,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,83</t>
+          <t>14,84; 25,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 24,95</t>
+          <t>11,21; 22,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 42,3</t>
+          <t>3,21; 27,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 28,93</t>
+          <t>18,05; 30,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,01; 25,93</t>
+          <t>16,08; 28,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 23,78</t>
+          <t>13,09; 24,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 24,42</t>
+          <t>8,3; 43,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 28,05</t>
+          <t>19,02; 28,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,62; 24,93</t>
+          <t>16,77; 25,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,36</t>
+          <t>13,3; 20,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 26,87</t>
+          <t>7,98; 27,36</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>18,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>17,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>18,76%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,88; 23,5</t>
+          <t>16,52; 25,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 22,42</t>
+          <t>11,5; 19,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 23,1</t>
+          <t>14,07; 22,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 35,1</t>
+          <t>17,08; 38,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 25,97</t>
+          <t>14,25; 24,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 19,44</t>
+          <t>12,92; 22,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,83; 22,32</t>
+          <t>15,2; 23,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 37,77</t>
+          <t>11,46; 42,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,36; 23,39</t>
+          <t>16,45; 23,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 19,2</t>
+          <t>13,27; 19,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,18; 21,11</t>
+          <t>15,24; 21,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,59; 32,34</t>
+          <t>17,48; 34,24</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24,99%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24,69%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,25%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,2%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,13; 31,2</t>
+          <t>14,4; 24,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,15; 24,64</t>
+          <t>15,12; 25,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,84</t>
+          <t>19,22; 31,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 36,41</t>
+          <t>5,45; 30,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 24,62</t>
+          <t>19,69; 31,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 25,41</t>
+          <t>14,35; 24,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 31,64</t>
+          <t>14,51; 24,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 30,88</t>
+          <t>11,83; 40,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,81; 25,55</t>
+          <t>17,98; 26,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,92</t>
+          <t>16,16; 23,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,43; 26,35</t>
+          <t>18,33; 26,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 27,84</t>
+          <t>10,65; 29,88</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>25,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 32,32</t>
+          <t>14,48; 23,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,1; 31,13</t>
+          <t>16,61; 26,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 24,79</t>
+          <t>14,93; 25,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 27,64</t>
+          <t>8,78; 35,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 24,05</t>
+          <t>20,78; 31,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 25,89</t>
+          <t>20,16; 30,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 24,68</t>
+          <t>15,09; 24,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 31,7</t>
+          <t>5,94; 29,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 26,65</t>
+          <t>19,1; 26,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,75; 26,83</t>
+          <t>20,17; 27,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,23; 23,47</t>
+          <t>16,51; 23,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 26,27</t>
+          <t>9,6; 25,96</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,62; 26,13</t>
+          <t>17,59; 22,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,71</t>
+          <t>16,73; 21,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,69</t>
+          <t>17,21; 22,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 26,48</t>
+          <t>14,2; 26,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,97</t>
+          <t>20,49; 26,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,46</t>
+          <t>18,62; 23,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,96</t>
+          <t>16,35; 21,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,96</t>
+          <t>13,93; 27,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 23,92</t>
+          <t>19,89; 23,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,91</t>
+          <t>18,19; 21,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,17</t>
+          <t>17,69; 21,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 23,52</t>
+          <t>15,77; 24,6</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29131</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28961</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22329</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>27715</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>28030</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>22040</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3751</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29131</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28961</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22329</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5646</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20941; 36364</t>
+          <t>22206; 36819</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20415; 35731</t>
+          <t>21569; 37143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15298; 30645</t>
+          <t>15167; 29903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1395; 7215</t>
+          <t>644; 5448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21847; 37322</t>
+          <t>20856; 35502</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21825; 37689</t>
+          <t>20652; 36927</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15476; 32187</t>
+          <t>16072; 30594</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>494; 5292</t>
+          <t>1422; 7535</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46420; 68584</t>
+          <t>46504; 68857</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45492; 68236</t>
+          <t>45900; 68723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34230; 55148</t>
+          <t>34343; 54192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3137; 10404</t>
+          <t>2968; 10173</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37528</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30505</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36982</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12208</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>30398</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>33269</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>36248</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5798</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37528</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30505</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36982</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>18300</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22947; 38864</t>
+          <t>29718; 46731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25972; 42540</t>
+          <t>23527; 40130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28274; 44638</t>
+          <t>29367; 46862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2989; 10170</t>
+          <t>7754; 17478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29791; 46724</t>
+          <t>23563; 39758</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22919; 39777</t>
+          <t>24511; 41871</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28864; 46594</t>
+          <t>29363; 45843</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8297; 18785</t>
+          <t>3088; 11383</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56502; 80774</t>
+          <t>56797; 80431</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52957; 75740</t>
+          <t>52321; 75314</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61019; 84834</t>
+          <t>61272; 84999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13058; 25457</t>
+          <t>12643; 24773</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25455</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31296</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35868</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>30759</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>27454</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>26308</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5640</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25455</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35868</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9977</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23829; 38870</t>
+          <t>19260; 33416</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20179; 35142</t>
+          <t>23519; 39329</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19878; 34041</t>
+          <t>27579; 44692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2546; 9553</t>
+          <t>1645; 9349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18857; 32940</t>
+          <t>24524; 39108</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24011; 39541</t>
+          <t>20458; 34944</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27904; 45407</t>
+          <t>19885; 33596</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1968; 9782</t>
+          <t>2805; 9709</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46010; 66005</t>
+          <t>46465; 67731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48179; 71329</t>
+          <t>48182; 70924</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51718; 73916</t>
+          <t>51422; 73672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5815; 16122</t>
+          <t>5742; 16106</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34451</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35856</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50768</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>51057</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>37533</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>34451</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35856</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9141</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42483; 62221</t>
+          <t>26247; 43099</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40655; 62967</t>
+          <t>33934; 54216</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29302; 46663</t>
+          <t>27222; 46355</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1756; 7753</t>
+          <t>2293; 9143</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26606; 43608</t>
+          <t>40002; 61140</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34324; 52874</t>
+          <t>40788; 61566</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27528; 45009</t>
+          <t>28400; 46572</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2603; 9038</t>
+          <t>1645; 8240</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72826; 99638</t>
+          <t>71395; 99409</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>80304; 109057</t>
+          <t>81990; 110550</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60152; 86972</t>
+          <t>61162; 86033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5647; 14860</t>
+          <t>5167; 13967</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>126565</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>134200</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123311; 156291</t>
+          <t>109774; 143230</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>122091; 157209</t>
+          <t>118759; 151405</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106331; 139069</t>
+          <t>115286; 148676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13605; 26560</t>
+          <t>17290; 32281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110984; 143305</t>
+          <t>122547; 156306</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>116359; 152330</t>
+          <t>123450; 156938</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>113675; 147131</t>
+          <t>104847; 137562</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18472; 32847</t>
+          <t>13305; 26436</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>245853; 292357</t>
+          <t>243041; 288656</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250288; 300829</t>
+          <t>249664; 300786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231019; 277629</t>
+          <t>231902; 275777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34095; 54546</t>
+          <t>34266; 53446</t>
         </is>
       </c>
     </row>
